--- a/artfynd/A 44790-2023 artfynd.xlsx
+++ b/artfynd/A 44790-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171162</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171130</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171154</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171165</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171153</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171166</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171132</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171164</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171161</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171149</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171156</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171150</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171169</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171159</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2456,6 +2536,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171151</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2579,6 +2664,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171148</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2690,6 +2780,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171168</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2801,6 +2896,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171170</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171133</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3023,6 +3128,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171134</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3134,6 +3244,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171155</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3245,6 +3360,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171163</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3356,8 +3476,39 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135171152</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44790-2023 artfynd.xlsx
+++ b/artfynd/A 44790-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135171162</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135171130</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135171154</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135171165</v>
       </c>
       <c r="B5" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135171153</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135171158</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135171166</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135171132</v>
       </c>
       <c r="B9" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135171164</v>
       </c>
       <c r="B10" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135171161</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135171149</v>
       </c>
       <c r="B12" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135171156</v>
       </c>
       <c r="B13" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135171150</v>
       </c>
       <c r="B14" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135171169</v>
       </c>
       <c r="B15" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135171159</v>
       </c>
       <c r="B16" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135171151</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>135171148</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135171168</v>
       </c>
       <c r="B19" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135171170</v>
       </c>
       <c r="B20" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135171133</v>
       </c>
       <c r="B21" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135171134</v>
       </c>
       <c r="B22" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135171155</v>
       </c>
       <c r="B23" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135171163</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135171152</v>
       </c>
       <c r="B25" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44790-2023 artfynd.xlsx
+++ b/artfynd/A 44790-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135171162</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135171130</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135171154</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135171165</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135171153</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135171158</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135171166</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135171132</v>
       </c>
       <c r="B9" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135171164</v>
       </c>
       <c r="B10" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135171161</v>
       </c>
       <c r="B11" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135171149</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135171156</v>
       </c>
       <c r="B13" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135171150</v>
       </c>
       <c r="B14" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135171169</v>
       </c>
       <c r="B15" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135171159</v>
       </c>
       <c r="B16" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135171168</v>
       </c>
       <c r="B19" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135171170</v>
       </c>
       <c r="B20" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135171133</v>
       </c>
       <c r="B21" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135171134</v>
       </c>
       <c r="B22" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135171155</v>
       </c>
       <c r="B23" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135171163</v>
       </c>
       <c r="B24" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135171152</v>
       </c>
       <c r="B25" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
